--- a/artfynd/A 6346-2025 artfynd.xlsx
+++ b/artfynd/A 6346-2025 artfynd.xlsx
@@ -880,7 +880,7 @@
         <v>126241513</v>
       </c>
       <c r="B4" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126241224</v>
       </c>
       <c r="B5" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126241482</v>
       </c>
       <c r="B7" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>126241516</v>
       </c>
       <c r="B8" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 6346-2025 artfynd.xlsx
+++ b/artfynd/A 6346-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126241463</v>
       </c>
       <c r="B2" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126241435</v>
       </c>
       <c r="B3" t="n">
-        <v>75068</v>
+        <v>75072</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126241513</v>
+        <v>126241224</v>
       </c>
       <c r="B4" t="n">
-        <v>91238</v>
+        <v>91256</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551978</v>
+        <v>552083</v>
       </c>
       <c r="R4" t="n">
-        <v>7038328</v>
+        <v>7038300</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126241224</v>
+        <v>126241513</v>
       </c>
       <c r="B5" t="n">
-        <v>91252</v>
+        <v>91242</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552083</v>
+        <v>551978</v>
       </c>
       <c r="R5" t="n">
-        <v>7038300</v>
+        <v>7038328</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1082,7 +1082,7 @@
         <v>126241494</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126241482</v>
       </c>
       <c r="B7" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>126241516</v>
       </c>
       <c r="B8" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 6346-2025 artfynd.xlsx
+++ b/artfynd/A 6346-2025 artfynd.xlsx
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126241224</v>
+        <v>126241513</v>
       </c>
       <c r="B4" t="n">
-        <v>91256</v>
+        <v>91242</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552083</v>
+        <v>551978</v>
       </c>
       <c r="R4" t="n">
-        <v>7038300</v>
+        <v>7038328</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126241513</v>
+        <v>126241224</v>
       </c>
       <c r="B5" t="n">
-        <v>91242</v>
+        <v>91256</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551978</v>
+        <v>552083</v>
       </c>
       <c r="R5" t="n">
-        <v>7038328</v>
+        <v>7038300</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 6346-2025 artfynd.xlsx
+++ b/artfynd/A 6346-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126241463</v>
       </c>
       <c r="B2" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126241435</v>
       </c>
       <c r="B3" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126241513</v>
       </c>
       <c r="B4" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126241224</v>
       </c>
       <c r="B5" t="n">
-        <v>91256</v>
+        <v>91259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>126241494</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126241482</v>
       </c>
       <c r="B7" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>126241516</v>
       </c>
       <c r="B8" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 6346-2025 artfynd.xlsx
+++ b/artfynd/A 6346-2025 artfynd.xlsx
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126241513</v>
+        <v>126241224</v>
       </c>
       <c r="B4" t="n">
-        <v>91245</v>
+        <v>91259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551978</v>
+        <v>552083</v>
       </c>
       <c r="R4" t="n">
-        <v>7038328</v>
+        <v>7038300</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126241224</v>
+        <v>126241513</v>
       </c>
       <c r="B5" t="n">
-        <v>91259</v>
+        <v>91245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552083</v>
+        <v>551978</v>
       </c>
       <c r="R5" t="n">
-        <v>7038300</v>
+        <v>7038328</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 6346-2025 artfynd.xlsx
+++ b/artfynd/A 6346-2025 artfynd.xlsx
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126241224</v>
+        <v>126241513</v>
       </c>
       <c r="B4" t="n">
-        <v>91259</v>
+        <v>91245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552083</v>
+        <v>551978</v>
       </c>
       <c r="R4" t="n">
-        <v>7038300</v>
+        <v>7038328</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126241513</v>
+        <v>126241224</v>
       </c>
       <c r="B5" t="n">
-        <v>91245</v>
+        <v>91259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551978</v>
+        <v>552083</v>
       </c>
       <c r="R5" t="n">
-        <v>7038328</v>
+        <v>7038300</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
